--- a/output/pdf_financials_xlsx/BU.xlsx
+++ b/output/pdf_financials_xlsx/BU.xlsx
@@ -6296,10 +6296,10 @@
         <v>0</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>0</v>
+        <v>0.00108</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>0</v>
+        <v>-0.080178</v>
       </c>
     </row>
     <row r="92">
@@ -12008,7 +12008,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -13380,7 +13384,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BU.xlsx
+++ b/output/pdf_financials_xlsx/BU.xlsx
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.077947</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.08761099999999999</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-4.811331</v>
+        <v>-4.889278</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-6.989116</v>
+        <v>-7.076727</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-8.806474</v>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-4.811331</v>
+        <v>-4.889278</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-6.989116</v>
+        <v>-7.076727</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-8.806474</v>
@@ -2625,16 +2625,16 @@
         <v>7.000824</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.456845</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>4.197141</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>7.275972</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.95053</v>
       </c>
     </row>
     <row r="35">
@@ -2747,16 +2747,16 @@
         <v>7.000824</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.456845</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>4.197141</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>7.275972</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.95053</v>
       </c>
     </row>
     <row r="37">
@@ -3479,16 +3479,16 @@
         <v>0.414328</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.200629</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>4.527174</v>
+        <v>0.330033</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>7.467362</v>
+        <v>0.19139</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>1.193722</v>
+        <v>0.243192</v>
       </c>
     </row>
     <row r="49">
@@ -8278,7 +8278,7 @@
         <v>0</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.09794600000000001</v>
       </c>
       <c r="P124" s="3" t="n">
         <v>0</v>
@@ -8339,7 +8339,7 @@
         <v>0</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.09794600000000001</v>
       </c>
       <c r="P125" s="3" t="n">
         <v>0</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -36454,7 +36454,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -63312,7 +63316,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -64898,7 +64902,7 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -67118,7 +67122,7 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
@@ -68610,7 +68614,7 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
@@ -73990,7 +73994,7 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E625" s="5" t="n">

--- a/output/pdf_financials_xlsx/BU.xlsx
+++ b/output/pdf_financials_xlsx/BU.xlsx
@@ -2238,13 +2238,13 @@
         <v>0</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.156036</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.239486</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.279277</v>
       </c>
       <c r="R28" s="1" t="inlineStr">
         <is>
@@ -2303,13 +2303,13 @@
         <v>-4.633494</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-10.258407</v>
+        <v>-10.102371</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-25.36425</v>
+        <v>-25.124764</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-7.446193</v>
+        <v>-7.166916</v>
       </c>
       <c r="R29" s="1" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>-1791.442357507945</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-5982.590058960407</v>
+        <v>-5891.591581083681</v>
       </c>
       <c r="P30" s="1" t="inlineStr">
         <is>
@@ -6812,13 +6812,13 @@
         <v>0</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.156036</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.239486</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.279277</v>
       </c>
       <c r="R100" s="3" t="n">
         <v>0</v>
@@ -7505,16 +7505,16 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.018574</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.000828</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.003745</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -7529,10 +7529,10 @@
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.019431</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.000476</v>
       </c>
       <c r="L112" s="3" t="n">
         <v>0</v>
@@ -30346,7 +30346,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -38196,7 +38200,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -39350,7 +39358,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -42856,7 +42868,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -43596,7 +43612,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E336" s="5" t="n">
         <v>0.018574</v>
       </c>
@@ -44124,7 +44144,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BU.xlsx
+++ b/output/pdf_financials_xlsx/BU.xlsx
@@ -4914,7 +4914,7 @@
         <v>0</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.014397</v>
       </c>
       <c r="P70" s="3" t="n">
         <v>0.034431</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.014397</v>
       </c>
       <c r="P71" s="3" t="n">
         <v>0.034431</v>
@@ -5219,7 +5219,7 @@
         <v>0.028431</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.014397</v>
+        <v>0</v>
       </c>
       <c r="P75" s="3" t="n">
         <v>0</v>
@@ -5553,10 +5553,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O80" s="3" t="n">
+        <v>0.0005096781136847352</v>
       </c>
       <c r="P80" s="3" t="n">
         <v>0.008322071993137573</v>
@@ -10848,7 +10846,11 @@
           <t>Lease liabilities 4, 11</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -15086,7 +15088,11 @@
           <t>Lease liabilities (note 10)</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -16702,7 +16708,11 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -25640,7 +25650,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
